--- a/dcf/MDB.xlsx
+++ b/dcf/MDB.xlsx
@@ -1148,184 +1148,184 @@
     </row>
     <row r="5">
       <c r="A5" s="53" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>72.12034559127417</v>
+        <v>106.5851312107165</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>70.32165915480357</v>
+        <v>103.2513442553617</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>68.6066098198495</v>
+        <v>100.0760724016902</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>66.97089260973058</v>
+        <v>97.05104394579463</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>65.41044382820643</v>
+        <v>94.16845511289823</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>63.92142648067851</v>
+        <v>91.42094159349118</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>62.50021663830425</v>
+        <v>88.80155192978908</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>75.56682415321842</v>
+        <v>110.0316097726608</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>73.6146276648594</v>
+        <v>106.5443127654175</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>71.75355607803357</v>
+        <v>103.2230186598743</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>69.97890774333699</v>
+        <v>100.059059079401</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>68.2862449566756</v>
+        <v>97.04425624136741</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>66.67137799195977</v>
+        <v>94.17089310477243</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>65.13035016745273</v>
+        <v>91.43168545893757</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="53" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>79.01330271516265</v>
+        <v>113.478088334605</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>76.90759617491521</v>
+        <v>109.8372812754733</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>74.90050233621764</v>
+        <v>106.3699649180583</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>72.9869228769434</v>
+        <v>103.0670742130074</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>71.16204608514479</v>
+        <v>99.9200573698366</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>69.42132950324104</v>
+        <v>96.92084461605371</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>67.76048369660121</v>
+        <v>94.06181898808605</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="53" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>82.45978127710688</v>
+        <v>116.9245668965493</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>80.20056468497101</v>
+        <v>113.1302497855291</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>78.0474485944017</v>
+        <v>109.5169111762424</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>75.9949380105498</v>
+        <v>106.0750893466139</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>74.03784721361397</v>
+        <v>102.7958584983058</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>72.17128101452231</v>
+        <v>99.67079612733498</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>70.39061722574971</v>
+        <v>96.69195251723455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="53" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>85.90625983905112</v>
+        <v>120.3710454584935</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>83.49353319502683</v>
+        <v>116.4232182955849</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>81.19439485258577</v>
+        <v>112.6638574344265</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>79.00295314415619</v>
+        <v>109.0831044802203</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>76.91364834208315</v>
+        <v>105.6716596267749</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>74.92123252580357</v>
+        <v>102.4207476386162</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>73.02075075489819</v>
+        <v>99.32208604638302</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="53" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>89.35273840099536</v>
+        <v>123.8175240204377</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>86.78650170508264</v>
+        <v>119.7161868056407</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>84.34134111076983</v>
+        <v>115.8108036926105</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>82.01096827776261</v>
+        <v>112.0911196138267</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>79.78944947055233</v>
+        <v>108.5474607552441</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>77.67118403708484</v>
+        <v>105.1706991498975</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>75.65088428404667</v>
+        <v>101.9522195755315</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="53" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>92.7992169629396</v>
+        <v>127.2640025823819</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>90.07947021513846</v>
+        <v>123.0091553156966</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>87.48828736895392</v>
+        <v>118.9577499507946</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>85.01898341136902</v>
+        <v>115.0991347474331</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>82.66525059902152</v>
+        <v>111.4232618837133</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>80.42113554836611</v>
+        <v>107.9206506611788</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>78.28101781319515</v>
+        <v>104.58235310468</v>
       </c>
     </row>
     <row r="13">
@@ -1348,7 +1348,7 @@
         <v>0.10987</v>
       </c>
       <c r="C14" s="57" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.5741179903297458</v>
+        <v>0.5284960358726299</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24427,7 +24427,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
@@ -24624,13 +24624,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>75.9949380105498</v>
+        <v>106.0750893466139</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>106.1141747079542</v>
+        <v>148.7868444805513</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>55.01621034757354</v>
+        <v>75.38696759119573</v>
       </c>
     </row>
     <row r="59">

--- a/dcf/MDB.xlsx
+++ b/dcf/MDB.xlsx
@@ -869,7 +869,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1151,25 +1151,25 @@
         <v>19</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>106.5851312107165</v>
+        <v>94.71175683874618</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>103.2513442553617</v>
+        <v>91.89283898160843</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>100.0760724016902</v>
+        <v>89.20771959486036</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>97.05104394579463</v>
+        <v>86.64942261162217</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>94.16845511289823</v>
+        <v>84.21136641706896</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>91.42094159349118</v>
+        <v>81.8873398609022</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>88.80155192978908</v>
+        <v>79.67147982886823</v>
       </c>
     </row>
     <row r="6">
@@ -1177,25 +1177,25 @@
         <v>20</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>110.0316097726608</v>
+        <v>97.61394028960122</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>106.5443127654175</v>
+        <v>94.66575590022681</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>103.2230186598743</v>
+        <v>91.85767524874954</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>100.059059079401</v>
+        <v>89.18238824125584</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>97.04425624136741</v>
+        <v>86.63299832134089</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>94.17089310477243</v>
+        <v>84.2029973133577</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>91.43168545893757</v>
+        <v>81.88624190112311</v>
       </c>
     </row>
     <row r="7">
@@ -1203,25 +1203,25 @@
         <v>21</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>113.478088334605</v>
+        <v>100.5161237404562</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>109.8372812754733</v>
+        <v>97.43867281884519</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>106.3699649180583</v>
+        <v>94.50763090263871</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>103.0670742130074</v>
+        <v>91.71535387088949</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>99.9200573698366</v>
+        <v>89.05463022561284</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>96.92084461605371</v>
+        <v>86.51865476581318</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>94.06181898808605</v>
+        <v>84.101003973378</v>
       </c>
     </row>
     <row r="8">
@@ -1229,25 +1229,25 @@
         <v>22</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>116.9245668965493</v>
+        <v>103.4183071913112</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>113.1302497855291</v>
+        <v>100.2115897374636</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>109.5169111762424</v>
+        <v>97.15758655652787</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>106.0750893466139</v>
+        <v>94.24831950052314</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>102.7958584983058</v>
+        <v>91.47626212988479</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>99.67079612733498</v>
+        <v>88.83431221826866</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>96.69195251723455</v>
+        <v>86.31576604563288</v>
       </c>
     </row>
     <row r="9">
@@ -1255,25 +1255,25 @@
         <v>23</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>120.3710454584935</v>
+        <v>106.3204906421662</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>116.4232182955849</v>
+        <v>102.9845066560819</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>112.6638574344265</v>
+        <v>99.80754221041704</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>109.0831044802203</v>
+        <v>96.78128513015679</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>105.6716596267749</v>
+        <v>93.89789403415671</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>102.4207476386162</v>
+        <v>91.14996967072415</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>99.32208604638302</v>
+        <v>88.53052811788777</v>
       </c>
     </row>
     <row r="10">
@@ -1281,25 +1281,25 @@
         <v>24</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>123.8175240204377</v>
+        <v>109.2226740930213</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>119.7161868056407</v>
+        <v>105.7574235747003</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>115.8108036926105</v>
+        <v>102.4574978643062</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>112.0911196138267</v>
+        <v>99.31425075979043</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>108.5474607552441</v>
+        <v>96.31952593842865</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>105.1706991498975</v>
+        <v>93.46562712317963</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>101.9522195755315</v>
+        <v>90.74529019014264</v>
       </c>
     </row>
     <row r="11">
@@ -1307,25 +1307,25 @@
         <v>25</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>127.2640025823819</v>
+        <v>112.1248575438763</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>123.0091553156966</v>
+        <v>108.5303404933187</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>118.9577499507946</v>
+        <v>105.1074535181954</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>115.0991347474331</v>
+        <v>101.8472163894241</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>111.4232618837133</v>
+        <v>98.7411578427006</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>107.9206506611788</v>
+        <v>95.78128457563513</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>104.58235310468</v>
+        <v>92.96005226239753</v>
       </c>
     </row>
     <row r="13">
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.5284960358726299</v>
+        <v>0.5409720073883493</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24472,7 +24472,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24624,13 +24624,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>106.0750893466139</v>
+        <v>94.24831950052314</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>148.7868444805513</v>
+        <v>128.2887924683928</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>75.38696759119573</v>
+        <v>69.07103102520206</v>
       </c>
     </row>
     <row r="59">
